--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484811_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484811_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>J. MAS MICO</t>
+          <t>P. TORMO HERRERO</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.8111</v>
+        <v>2.8133</v>
       </c>
       <c r="E2" t="n">
-        <v>1.27</v>
+        <v>0.2892</v>
       </c>
       <c r="F2" t="n">
-        <v>1.5411</v>
+        <v>2.5241</v>
       </c>
       <c r="G2" t="n">
-        <v>0.843</v>
+        <v>4.2107</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.7396</v>
+        <v>1.141</v>
       </c>
       <c r="I2" t="n">
-        <v>1.5825</v>
+        <v>3.0697</v>
       </c>
       <c r="J2" t="n">
-        <v>1.4558</v>
+        <v>3.2372</v>
       </c>
       <c r="K2" t="n">
-        <v>0.09</v>
+        <v>1.3367</v>
       </c>
       <c r="L2" t="n">
-        <v>1.3658</v>
+        <v>1.9005</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.6128</v>
+        <v>0.9736</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.8295</v>
+        <v>-0.1956</v>
       </c>
       <c r="O2" t="n">
-        <v>0.2167</v>
+        <v>1.1692</v>
       </c>
       <c r="P2" t="n">
-        <v>0.9435</v>
+        <v>-1.1322</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.1887</v>
+        <v>-2.8305</v>
       </c>
       <c r="R2" t="n">
-        <v>1.1322</v>
+        <v>1.6983</v>
       </c>
       <c r="S2" t="n">
-        <v>1.0246</v>
+        <v>-0.2653</v>
       </c>
       <c r="T2" t="n">
-        <v>0.0029</v>
+        <v>-0.4193</v>
       </c>
       <c r="U2" t="n">
-        <v>1.0217</v>
+        <v>0.154</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>0.3018</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>-0.3018</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>P. TORMO HERRERO</t>
+          <t>J. MAS MICO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.4248</v>
+        <v>2.4021</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1917</v>
+        <v>1.2314</v>
       </c>
       <c r="F3" t="n">
-        <v>2.2331</v>
+        <v>1.1707</v>
       </c>
       <c r="G3" t="n">
-        <v>4.2107</v>
+        <v>0.843</v>
       </c>
       <c r="H3" t="n">
-        <v>1.141</v>
+        <v>-0.7396</v>
       </c>
       <c r="I3" t="n">
-        <v>3.0697</v>
+        <v>1.5825</v>
       </c>
       <c r="J3" t="n">
-        <v>3.2372</v>
+        <v>1.4558</v>
       </c>
       <c r="K3" t="n">
-        <v>1.3367</v>
+        <v>0.09</v>
       </c>
       <c r="L3" t="n">
-        <v>1.9005</v>
+        <v>1.3658</v>
       </c>
       <c r="M3" t="n">
-        <v>0.9736</v>
+        <v>-0.6128</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.1956</v>
+        <v>-0.8295</v>
       </c>
       <c r="O3" t="n">
-        <v>1.1692</v>
+        <v>0.2167</v>
       </c>
       <c r="P3" t="n">
-        <v>-1.1322</v>
+        <v>0.9435</v>
       </c>
       <c r="Q3" t="n">
-        <v>-2.8305</v>
+        <v>-0.1887</v>
       </c>
       <c r="R3" t="n">
-        <v>1.6983</v>
+        <v>1.1322</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.6536999999999999</v>
+        <v>0.6156</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.5168</v>
+        <v>-0.0357</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.137</v>
+        <v>0.6514</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>0.3018</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.3018</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.971</v>
+        <v>1.9936</v>
       </c>
       <c r="E4" t="n">
-        <v>1.1162</v>
+        <v>0.9801</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8548</v>
+        <v>1.0136</v>
       </c>
       <c r="G4" t="n">
         <v>3.4403</v>
@@ -766,13 +766,13 @@
         <v>1.3209</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.5067</v>
+        <v>-0.4841</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.6438</v>
+        <v>-0.7798</v>
       </c>
       <c r="U4" t="n">
-        <v>0.137</v>
+        <v>0.2958</v>
       </c>
       <c r="V4" t="n">
         <v>0.9244</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.5599</v>
+        <v>0.7064</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.7135</v>
+        <v>-0.7522</v>
       </c>
       <c r="F5" t="n">
-        <v>1.2734</v>
+        <v>1.4586</v>
       </c>
       <c r="G5" t="n">
         <v>0.223</v>
@@ -844,13 +844,13 @@
         <v>1.1322</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.418</v>
+        <v>-0.2714</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.4674</v>
+        <v>-0.506</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0494</v>
+        <v>0.2346</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.1573</v>
+        <v>-0.0347</v>
       </c>
       <c r="E6" t="n">
-        <v>-2.8384</v>
+        <v>-2.2925</v>
       </c>
       <c r="F6" t="n">
-        <v>2.6811</v>
+        <v>2.2578</v>
       </c>
       <c r="G6" t="n">
         <v>0.9011</v>
@@ -922,13 +922,13 @@
         <v>1.887</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.3221</v>
+        <v>-0.1994</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.4109</v>
+        <v>-0.8649</v>
       </c>
       <c r="U6" t="n">
-        <v>1.0888</v>
+        <v>0.6655</v>
       </c>
       <c r="V6" t="n">
         <v>1.528</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.2721</v>
+        <v>-0.1398</v>
       </c>
       <c r="E7" t="n">
         <v>-0.1194</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.1527</v>
+        <v>-0.0204</v>
       </c>
       <c r="G7" t="n">
         <v>0.6716</v>
@@ -1000,13 +1000,13 @@
         <v>0.5661</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.2645</v>
+        <v>-0.1323</v>
       </c>
       <c r="T7" t="n">
         <v>-0.2228</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.0417</v>
+        <v>0.0905</v>
       </c>
       <c r="V7" t="n">
         <v>-1.2452</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.5576</v>
+        <v>-0.4253</v>
       </c>
       <c r="E8" t="n">
         <v>-1.7335</v>
       </c>
       <c r="F8" t="n">
-        <v>1.1759</v>
+        <v>1.3082</v>
       </c>
       <c r="G8" t="n">
         <v>-0.05</v>
@@ -1078,13 +1078,13 @@
         <v>0.7548</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.7719</v>
+        <v>-0.6395999999999999</v>
       </c>
       <c r="T8" t="n">
         <v>-0.6931</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.07870000000000001</v>
+        <v>0.0535</v>
       </c>
       <c r="V8" t="n">
         <v>-0.3018</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.5841</v>
+        <v>-0.5048</v>
       </c>
       <c r="E9" t="n">
         <v>-0.1929</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.3913</v>
+        <v>-0.3119</v>
       </c>
       <c r="G9" t="n">
         <v>-0.1421</v>
@@ -1156,13 +1156,13 @@
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.4421</v>
+        <v>-0.3627</v>
       </c>
       <c r="T9" t="n">
         <v>-0.2352</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2069</v>
+        <v>-0.1276</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>F. LOPEZ ZOROA</t>
+          <t>M. PEREZ MARCO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.9141</v>
+        <v>-0.8504</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.9963</v>
+        <v>-0.9012</v>
       </c>
       <c r="F10" t="n">
-        <v>1.0822</v>
+        <v>0.0508</v>
       </c>
       <c r="G10" t="n">
-        <v>0.1323</v>
+        <v>-0.6617</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.1512</v>
+        <v>-0.2504</v>
       </c>
       <c r="I10" t="n">
-        <v>1.2836</v>
+        <v>-0.4113</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.9555</v>
+        <v>-0.6073</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.5895</v>
+        <v>-0.6073</v>
       </c>
       <c r="L10" t="n">
-        <v>0.634</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>1.0878</v>
+        <v>-0.0544</v>
       </c>
       <c r="N10" t="n">
-        <v>0.4383</v>
+        <v>0.3569</v>
       </c>
       <c r="O10" t="n">
-        <v>0.6496</v>
+        <v>-0.4113</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>0.1887</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.9435</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>0.9435</v>
+        <v>0.1887</v>
       </c>
       <c r="S10" t="n">
-        <v>0.1987</v>
+        <v>-0.3774</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.3992</v>
+        <v>-0.2939</v>
       </c>
       <c r="U10" t="n">
-        <v>0.5979</v>
+        <v>-0.0835</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.2452</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>0.3018</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.547</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>M. PEREZ MARCO</t>
+          <t>F. LOPEZ ZOROA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.9562</v>
+        <v>-1.0896</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.9012</v>
+        <v>-1.8015</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.055</v>
+        <v>0.7118</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.6617</v>
+        <v>0.1323</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.2504</v>
+        <v>-1.1512</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.4113</v>
+        <v>1.2836</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.6073</v>
+        <v>-0.9555</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.6073</v>
+        <v>-1.5895</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>0.634</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.0544</v>
+        <v>1.0878</v>
       </c>
       <c r="N11" t="n">
-        <v>0.3569</v>
+        <v>0.4383</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.4113</v>
+        <v>0.6496</v>
       </c>
       <c r="P11" t="n">
-        <v>0.1887</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>-0.9435</v>
       </c>
       <c r="R11" t="n">
-        <v>0.1887</v>
+        <v>0.9435</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.4832</v>
+        <v>0.0232</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.2939</v>
+        <v>-0.2043</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1893</v>
+        <v>0.2275</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>-1.2452</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>0.3018</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>-1.547</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.7564</v>
+        <v>-1.517</v>
       </c>
       <c r="E12" t="n">
-        <v>-5.2726</v>
+        <v>-4.9803</v>
       </c>
       <c r="F12" t="n">
-        <v>3.5163</v>
+        <v>3.4633</v>
       </c>
       <c r="G12" t="n">
         <v>-2.6818</v>
@@ -1390,13 +1390,13 @@
         <v>2.4531</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.6972</v>
+        <v>-0.4578</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.3398</v>
+        <v>-1.0475</v>
       </c>
       <c r="U12" t="n">
-        <v>0.6425999999999999</v>
+        <v>0.5897</v>
       </c>
       <c r="V12" t="n">
         <v>1.2452</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-2.5314</v>
+        <v>-3.0224</v>
       </c>
       <c r="E13" t="n">
-        <v>0.7727000000000001</v>
+        <v>0.1495</v>
       </c>
       <c r="F13" t="n">
-        <v>-3.3041</v>
+        <v>-3.1718</v>
       </c>
       <c r="G13" t="n">
         <v>0.1187</v>
@@ -1468,13 +1468,13 @@
         <v>1.1322</v>
       </c>
       <c r="S13" t="n">
-        <v>0.4438</v>
+        <v>-0.0472</v>
       </c>
       <c r="T13" t="n">
-        <v>0.7112000000000001</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.2674</v>
+        <v>-0.1352</v>
       </c>
       <c r="V13" t="n">
         <v>-4.0374</v>
@@ -1501,10 +1501,10 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>0.03759999999999986</v>
+        <v>0.3313999999999999</v>
       </c>
       <c r="E14" t="n">
-        <v>-10.4172</v>
+        <v>-10.1233</v>
       </c>
       <c r="F14" t="n">
         <v>10.4548</v>
@@ -1519,7 +1519,7 @@
         <v>12.1234</v>
       </c>
       <c r="J14" t="n">
-        <v>4.338900000000001</v>
+        <v>4.338899999999999</v>
       </c>
       <c r="K14" t="n">
         <v>-3.5609</v>
@@ -1534,7 +1534,7 @@
         <v>-1.5571</v>
       </c>
       <c r="O14" t="n">
-        <v>4.223400000000001</v>
+        <v>4.2234</v>
       </c>
       <c r="P14" t="n">
         <v>-0.9435000000000002</v>
@@ -1546,13 +1546,13 @@
         <v>13.209</v>
       </c>
       <c r="S14" t="n">
-        <v>-2.8923</v>
+        <v>-2.5984</v>
       </c>
       <c r="T14" t="n">
-        <v>-5.5088</v>
+        <v>-5.2145</v>
       </c>
       <c r="U14" t="n">
-        <v>2.6164</v>
+        <v>2.6162</v>
       </c>
       <c r="V14" t="n">
         <v>-3.132</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>8.635199999999999</v>
+        <v>7.4673</v>
       </c>
       <c r="E15" t="n">
-        <v>4.9543</v>
+        <v>4.0774</v>
       </c>
       <c r="F15" t="n">
-        <v>3.6809</v>
+        <v>3.3899</v>
       </c>
       <c r="G15" t="n">
         <v>-2.0343</v>
@@ -1624,13 +1624,13 @@
         <v>2.8305</v>
       </c>
       <c r="S15" t="n">
-        <v>2.1415</v>
+        <v>0.9736</v>
       </c>
       <c r="T15" t="n">
-        <v>0.5748</v>
+        <v>-0.3021</v>
       </c>
       <c r="U15" t="n">
-        <v>1.5667</v>
+        <v>1.2757</v>
       </c>
       <c r="V15" t="n">
         <v>6.8296</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>M. MARTIN MARTINEZ</t>
+          <t>B. TERREROS RIVAS</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.7366</v>
+        <v>1.7564</v>
       </c>
       <c r="E16" t="n">
-        <v>0.3637</v>
+        <v>-1.1112</v>
       </c>
       <c r="F16" t="n">
-        <v>1.3729</v>
+        <v>2.8677</v>
       </c>
       <c r="G16" t="n">
-        <v>0.1898</v>
+        <v>1.2148</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.241</v>
+        <v>2.9097</v>
       </c>
       <c r="I16" t="n">
-        <v>0.4309</v>
+        <v>-1.6949</v>
       </c>
       <c r="J16" t="n">
-        <v>0.1257</v>
+        <v>1.9311</v>
       </c>
       <c r="K16" t="n">
-        <v>0.08450000000000001</v>
+        <v>2.4573</v>
       </c>
       <c r="L16" t="n">
-        <v>0.0411</v>
+        <v>-0.5262</v>
       </c>
       <c r="M16" t="n">
-        <v>0.06419999999999999</v>
+        <v>-0.7163</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.3256</v>
+        <v>0.4524</v>
       </c>
       <c r="O16" t="n">
-        <v>0.3897</v>
+        <v>-1.1687</v>
       </c>
       <c r="P16" t="n">
-        <v>0.5661</v>
+        <v>0.7548</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.1887</v>
+        <v>-2.0757</v>
       </c>
       <c r="R16" t="n">
-        <v>0.7548</v>
+        <v>2.8305</v>
       </c>
       <c r="S16" t="n">
-        <v>0.9617</v>
+        <v>0.4284</v>
       </c>
       <c r="T16" t="n">
-        <v>0.4267</v>
+        <v>-0.6269</v>
       </c>
       <c r="U16" t="n">
-        <v>0.535</v>
+        <v>1.0553</v>
       </c>
       <c r="V16" t="n">
-        <v>0.019</v>
+        <v>-0.6415999999999999</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>-0.3398</v>
       </c>
       <c r="X16" t="n">
-        <v>0.019</v>
+        <v>-0.3018</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>B. TERREROS RIVAS</t>
+          <t>M. MARTIN MARTINEZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.5532</v>
+        <v>1.365</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.2087</v>
+        <v>0.07140000000000001</v>
       </c>
       <c r="F17" t="n">
-        <v>2.7618</v>
+        <v>1.2936</v>
       </c>
       <c r="G17" t="n">
-        <v>1.2148</v>
+        <v>0.1898</v>
       </c>
       <c r="H17" t="n">
-        <v>2.9097</v>
+        <v>-0.241</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.6949</v>
+        <v>0.4309</v>
       </c>
       <c r="J17" t="n">
-        <v>1.9311</v>
+        <v>0.1257</v>
       </c>
       <c r="K17" t="n">
-        <v>2.4573</v>
+        <v>0.08450000000000001</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.5262</v>
+        <v>0.0411</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.7163</v>
+        <v>0.06419999999999999</v>
       </c>
       <c r="N17" t="n">
-        <v>0.4524</v>
+        <v>-0.3256</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.1687</v>
+        <v>0.3897</v>
       </c>
       <c r="P17" t="n">
+        <v>0.5661</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>-0.1887</v>
+      </c>
+      <c r="R17" t="n">
         <v>0.7548</v>
       </c>
-      <c r="Q17" t="n">
-        <v>-2.0757</v>
-      </c>
-      <c r="R17" t="n">
-        <v>2.8305</v>
-      </c>
       <c r="S17" t="n">
-        <v>0.2251</v>
+        <v>0.59</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.7243000000000001</v>
+        <v>0.1344</v>
       </c>
       <c r="U17" t="n">
-        <v>0.9495</v>
+        <v>0.4556</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.6415999999999999</v>
+        <v>0.019</v>
       </c>
       <c r="W17" t="n">
-        <v>-0.3398</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.3018</v>
+        <v>0.019</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. NÚÑEZ NIEVAS</t>
+          <t>J. NUNEZ NIEVAS</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.9509</v>
+        <v>1.3064</v>
       </c>
       <c r="E18" t="n">
-        <v>0.9509</v>
+        <v>-0.4131</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>1.7195</v>
       </c>
       <c r="G18" t="n">
-        <v>0.9509</v>
+        <v>-2.7017</v>
       </c>
       <c r="H18" t="n">
-        <v>0.9509</v>
+        <v>-0.8875</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>-1.8142</v>
       </c>
       <c r="J18" t="n">
-        <v>0.9509</v>
+        <v>-1.3471</v>
       </c>
       <c r="K18" t="n">
-        <v>0.9509</v>
+        <v>-1.3727</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>0.0256</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>-1.3546</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>0.4852</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>-1.8398</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>2.4531</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-0.1887</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>2.6418</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>0.6116</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>-0.4242</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1.0359</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>0.9434</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.547</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-0.6036</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.8673</v>
+        <v>1.0357</v>
       </c>
       <c r="E19" t="n">
-        <v>0.7141999999999999</v>
+        <v>0.9091</v>
       </c>
       <c r="F19" t="n">
-        <v>0.153</v>
+        <v>0.1266</v>
       </c>
       <c r="G19" t="n">
         <v>-0.1762</v>
@@ -1936,13 +1936,13 @@
         <v>0.7548</v>
       </c>
       <c r="S19" t="n">
-        <v>0.2886</v>
+        <v>0.4571</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.0465</v>
+        <v>0.1484</v>
       </c>
       <c r="U19" t="n">
-        <v>0.3351</v>
+        <v>0.3086</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. NUNEZ NIEVAS</t>
+          <t>J. NÚÑEZ NIEVAS</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.3009</v>
+        <v>0.9509</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.9977</v>
+        <v>0.9509</v>
       </c>
       <c r="F20" t="n">
-        <v>1.2986</v>
+        <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.7017</v>
+        <v>0.9509</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.8875</v>
+        <v>0.9509</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.8142</v>
+        <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.3471</v>
+        <v>0.9509</v>
       </c>
       <c r="K20" t="n">
-        <v>-1.3727</v>
+        <v>0.9509</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0256</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.3546</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>0.4852</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.8398</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>2.4531</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.1887</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>2.6418</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.3939</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.0088</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>0.615</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>0.9434</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>1.547</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.6036</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.1787</v>
+        <v>-0.02</v>
       </c>
       <c r="E21" t="n">
         <v>-1.0188</v>
       </c>
       <c r="F21" t="n">
-        <v>0.8401</v>
+        <v>0.9988</v>
       </c>
       <c r="G21" t="n">
         <v>0.2692</v>
@@ -2092,13 +2092,13 @@
         <v>0.3774</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.8253</v>
+        <v>-0.6666</v>
       </c>
       <c r="T21" t="n">
         <v>-0.4115</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.4138</v>
+        <v>-0.2551</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.063</v>
+        <v>-0.6143999999999999</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.4321</v>
+        <v>-1.1398</v>
       </c>
       <c r="F22" t="n">
-        <v>0.369</v>
+        <v>0.5254</v>
       </c>
       <c r="G22" t="n">
         <v>-0.7056</v>
@@ -2170,13 +2170,13 @@
         <v>0.7548</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.301</v>
+        <v>0.1477</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.3868</v>
+        <v>-0.0945</v>
       </c>
       <c r="U22" t="n">
-        <v>0.0859</v>
+        <v>0.2422</v>
       </c>
       <c r="V22" t="n">
         <v>-0.6226</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.2653</v>
+        <v>-1.9321</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.5807</v>
+        <v>-1.4833</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.6846</v>
+        <v>-0.4488</v>
       </c>
       <c r="G23" t="n">
         <v>-0.6711</v>
@@ -2248,13 +2248,13 @@
         <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.047</v>
+        <v>0.2861</v>
       </c>
       <c r="T23" t="n">
-        <v>0.0123</v>
+        <v>0.1098</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.0594</v>
+        <v>0.1764</v>
       </c>
       <c r="V23" t="n">
         <v>-0.6036</v>
@@ -2269,7 +2269,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>M. FERNANDEZ CARRASCO</t>
+          <t>G. GARCIA CARCASES</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,73 +2281,73 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.1555</v>
+        <v>-5.2097</v>
       </c>
       <c r="E24" t="n">
-        <v>-5.9937</v>
+        <v>-5.2063</v>
       </c>
       <c r="F24" t="n">
-        <v>0.8381999999999999</v>
+        <v>-0.0034</v>
       </c>
       <c r="G24" t="n">
-        <v>-2.2512</v>
+        <v>-1.0899</v>
       </c>
       <c r="H24" t="n">
-        <v>0.7192</v>
+        <v>0.9822</v>
       </c>
       <c r="I24" t="n">
-        <v>-2.9704</v>
+        <v>-2.0721</v>
       </c>
       <c r="J24" t="n">
-        <v>-1.081</v>
+        <v>-0.5750999999999999</v>
       </c>
       <c r="K24" t="n">
-        <v>0.2011</v>
+        <v>0.09</v>
       </c>
       <c r="L24" t="n">
-        <v>-1.2821</v>
+        <v>-0.6651</v>
       </c>
       <c r="M24" t="n">
-        <v>-1.1702</v>
+        <v>-0.5148</v>
       </c>
       <c r="N24" t="n">
-        <v>0.5181</v>
+        <v>0.8922</v>
       </c>
       <c r="O24" t="n">
-        <v>-1.6883</v>
+        <v>-1.4069</v>
       </c>
       <c r="P24" t="n">
         <v>-2.6418</v>
       </c>
       <c r="Q24" t="n">
-        <v>-4.7175</v>
+        <v>-3.774</v>
       </c>
       <c r="R24" t="n">
-        <v>2.0757</v>
+        <v>1.1322</v>
       </c>
       <c r="S24" t="n">
-        <v>1.2845</v>
+        <v>-0.2328</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.1952</v>
+        <v>-0.8571</v>
       </c>
       <c r="U24" t="n">
-        <v>1.4797</v>
+        <v>0.6243</v>
       </c>
       <c r="V24" t="n">
-        <v>-1.547</v>
+        <v>-1.2452</v>
       </c>
       <c r="W24" t="n">
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-1.547</v>
+        <v>-1.2452</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>G. GARCIA CARCASES</t>
+          <t>M. FERNANDEZ CARRASCO</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-5.419</v>
+        <v>-5.4934</v>
       </c>
       <c r="E25" t="n">
-        <v>-5.2063</v>
+        <v>-6.0911</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.2127</v>
+        <v>0.5977</v>
       </c>
       <c r="G25" t="n">
-        <v>-1.0899</v>
+        <v>-2.2512</v>
       </c>
       <c r="H25" t="n">
-        <v>0.9822</v>
+        <v>0.7192</v>
       </c>
       <c r="I25" t="n">
-        <v>-2.0721</v>
+        <v>-2.9704</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.5750999999999999</v>
+        <v>-1.081</v>
       </c>
       <c r="K25" t="n">
-        <v>0.09</v>
+        <v>0.2011</v>
       </c>
       <c r="L25" t="n">
-        <v>-0.6651</v>
+        <v>-1.2821</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.5148</v>
+        <v>-1.1702</v>
       </c>
       <c r="N25" t="n">
-        <v>0.8922</v>
+        <v>0.5181</v>
       </c>
       <c r="O25" t="n">
-        <v>-1.4069</v>
+        <v>-1.6883</v>
       </c>
       <c r="P25" t="n">
         <v>-2.6418</v>
       </c>
       <c r="Q25" t="n">
-        <v>-3.774</v>
+        <v>-4.7175</v>
       </c>
       <c r="R25" t="n">
-        <v>1.1322</v>
+        <v>2.0757</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.4421</v>
+        <v>0.9466</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.8571</v>
+        <v>-0.2927</v>
       </c>
       <c r="U25" t="n">
-        <v>0.4151</v>
+        <v>1.2393</v>
       </c>
       <c r="V25" t="n">
-        <v>-1.2452</v>
+        <v>-1.547</v>
       </c>
       <c r="W25" t="n">
         <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>-1.2452</v>
+        <v>-1.547</v>
       </c>
     </row>
     <row r="26">
@@ -2437,16 +2437,16 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.03740000000000077</v>
+        <v>0.612099999999999</v>
       </c>
       <c r="E26" t="n">
-        <v>-10.4549</v>
+        <v>-10.4548</v>
       </c>
       <c r="F26" t="n">
-        <v>10.4172</v>
+        <v>11.067</v>
       </c>
       <c r="G26" t="n">
-        <v>-7.0053</v>
+        <v>-7.005300000000001</v>
       </c>
       <c r="H26" t="n">
         <v>5.1182</v>
@@ -2482,13 +2482,13 @@
         <v>14.1525</v>
       </c>
       <c r="S26" t="n">
-        <v>2.8921</v>
+        <v>3.541700000000001</v>
       </c>
       <c r="T26" t="n">
         <v>-2.6164</v>
       </c>
       <c r="U26" t="n">
-        <v>5.5088</v>
+        <v>6.1582</v>
       </c>
       <c r="V26" t="n">
         <v>3.132000000000001</v>
